--- a/서버정보/20260901_리소스배포_운영.xlsx
+++ b/서버정보/20260901_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEF03D1-C16B-40EC-B5BB-EF9DB929BF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DD4CF9-149B-4DB1-86EF-B47F2200E515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -5763,11 +5763,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.158.50.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-p-sec-mevrsol-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.150.10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6312,7 +6312,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6685,17 +6685,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -26488,11 +26479,11 @@
       <c r="B146" s="95" t="s">
         <v>1095</v>
       </c>
-      <c r="C146" s="124" t="str" cm="1">
+      <c r="C146" s="95" t="str" cm="1">
         <f t="array" ref="C146">UPPER(INDEX(_xlfn.TEXTSPLIT($F146, "-"), 3))</f>
         <v>SEC</v>
       </c>
-      <c r="D146" s="124" t="s">
+      <c r="D146" s="95" t="s">
         <v>1096</v>
       </c>
       <c r="E146" s="95" t="s">
@@ -26522,10 +26513,10 @@
       <c r="M146" s="95" t="s">
         <v>1101</v>
       </c>
-      <c r="N146" s="125" t="s">
+      <c r="N146" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O146" s="126" t="str">
+      <c r="O146" s="123" t="str">
         <f>SUBSTITUTE(F146,"hazr-","")&amp;"-osdisk"</f>
         <v>p-sec-mevrsol01-osdisk</v>
       </c>
@@ -26535,10 +26526,10 @@
       <c r="Q146" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R146" s="124"/>
+      <c r="R146" s="95"/>
       <c r="S146" s="95"/>
-      <c r="T146" s="124"/>
-      <c r="U146" s="124" t="str">
+      <c r="T146" s="95"/>
+      <c r="U146" s="95" t="str">
         <f>SUBSTITUTE(F146,"hazr-","")&amp;"-nic"</f>
         <v>p-sec-mevrsol01-nic</v>
       </c>
@@ -26576,11 +26567,11 @@
       <c r="B147" s="95" t="s">
         <v>1095</v>
       </c>
-      <c r="C147" s="124" t="str" cm="1">
+      <c r="C147" s="95" t="str" cm="1">
         <f t="array" ref="C147">UPPER(INDEX(_xlfn.TEXTSPLIT($F147, "-"), 3))</f>
         <v>SEC</v>
       </c>
-      <c r="D147" s="124" t="s">
+      <c r="D147" s="95" t="s">
         <v>1096</v>
       </c>
       <c r="E147" s="95" t="s">
@@ -26610,10 +26601,10 @@
       <c r="M147" s="95" t="s">
         <v>1101</v>
       </c>
-      <c r="N147" s="125" t="s">
+      <c r="N147" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O147" s="126" t="str">
+      <c r="O147" s="123" t="str">
         <f>SUBSTITUTE(F147,"hazr-","")&amp;"-osdisk"</f>
         <v>p-sec-mevrsol02-osdisk</v>
       </c>
@@ -26623,10 +26614,10 @@
       <c r="Q147" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R147" s="124"/>
+      <c r="R147" s="95"/>
       <c r="S147" s="95"/>
-      <c r="T147" s="124"/>
-      <c r="U147" s="124" t="str">
+      <c r="T147" s="95"/>
+      <c r="U147" s="95" t="str">
         <f>SUBSTITUTE(F147,"hazr-","")&amp;"-nic"</f>
         <v>p-sec-mevrsol02-nic</v>
       </c>
@@ -46333,26 +46324,26 @@
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="127" t="s">
+      <c r="B45" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="C45" s="127" t="str" cm="1">
+      <c r="C45" s="74" t="str" cm="1">
         <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($F45, "-"), 3))</f>
         <v>SEC</v>
       </c>
-      <c r="D45" s="127" t="s">
+      <c r="D45" s="74" t="s">
         <v>1096</v>
       </c>
-      <c r="E45" s="127" t="s">
+      <c r="E45" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="127" t="s">
+      <c r="F45" s="74" t="s">
         <v>1112</v>
       </c>
-      <c r="G45" s="127" t="s">
+      <c r="G45" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="H45" s="127" t="s">
+      <c r="H45" s="74" t="s">
         <v>1016</v>
       </c>
       <c r="I45" s="74" t="s">
@@ -46361,24 +46352,24 @@
       <c r="J45" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="K45" s="127" t="str">
+      <c r="K45" s="74" t="str">
         <f t="shared" si="5"/>
         <v>p-sec-mevrsol-lb-fe</v>
       </c>
-      <c r="L45" s="127" t="s">
+      <c r="L45" s="74" t="s">
         <v>1113</v>
       </c>
-      <c r="M45" s="127" t="s">
+      <c r="M45" s="74" t="s">
         <v>1107</v>
       </c>
-      <c r="N45" s="127" t="s">
+      <c r="N45" s="74" t="s">
         <v>1108</v>
       </c>
-      <c r="O45" s="127" t="s">
+      <c r="O45" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P45" s="127" t="s">
-        <v>1114</v>
+      <c r="P45" s="74" t="s">
+        <v>1115</v>
       </c>
       <c r="Q45" s="74" t="str">
         <f t="shared" si="6"/>
@@ -48577,7 +48568,7 @@
         <v>1110</v>
       </c>
       <c r="E67" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F67" s="74" t="str">
         <f t="shared" si="15"/>
@@ -48609,7 +48600,7 @@
         <v>1110</v>
       </c>
       <c r="E68" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F68" s="74" t="str">
         <f t="shared" si="15"/>
@@ -48641,7 +48632,7 @@
         <v>1110</v>
       </c>
       <c r="E69" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F69" s="74" t="str">
         <f t="shared" si="15"/>
@@ -48673,7 +48664,7 @@
         <v>1110</v>
       </c>
       <c r="E70" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F70" s="74" t="str">
         <f t="shared" si="15"/>
@@ -48705,7 +48696,7 @@
         <v>1110</v>
       </c>
       <c r="E71" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F71" s="74" t="str">
         <f t="shared" si="15"/>
@@ -48737,7 +48728,7 @@
         <v>1110</v>
       </c>
       <c r="E72" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F72" s="74" t="str">
         <f t="shared" si="15"/>
@@ -48764,21 +48755,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -48922,10 +48898,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -48947,19 +48948,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>